--- a/Result/profitability/6590.xlsx
+++ b/Result/profitability/6590.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM42"/>
+  <dimension ref="A1:AM43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5764,6 +5764,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6590</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>209</v>
+      </c>
+      <c r="D43" t="n">
+        <v>125</v>
+      </c>
+      <c r="E43" t="n">
+        <v>84</v>
+      </c>
+      <c r="F43" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>13.71%</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>23</v>
+      </c>
+      <c r="J43" t="n">
+        <v>52</v>
+      </c>
+      <c r="K43" t="n">
+        <v>41</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.3225</v>
+      </c>
+      <c r="N43" t="n">
+        <v>45.09125</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-3.640000000000001</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-0.0830102622576967</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-0.1100000000000001</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-0.0617977528089888</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>-7.359999999999999</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-0.15471936094177</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
